--- a/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/03_MAI3 - Müşteri ve Üretim Takımları/EKG-BAK-LST-03_takim_ana_listesi_ve_omur_takip_karti.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/11_Bakım, Yedek Parça ve Takımlar/03_MAI3 - Müşteri ve Üretim Takımları/EKG-BAK-LST-03_takim_ana_listesi_ve_omur_takip_karti.xlsx
@@ -903,7 +903,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-LST-03&amp;C&amp;"Arial,Regular"&amp;11Takım Ana Listesi ve Ömür Takip Kartı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 24.09.2026
+Revizyon nedeni: Takım listesine mülkiyet, konum ve birimli ömür hesabı; geçmiş kartına bakım ve doğrulama kaydı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1086,7 +1087,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-BAK-LST-03&amp;C&amp;"Arial,Regular"&amp;11Takım Ana Listesi ve Ömür Takip Kartı</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 24.09.2026
+Revizyon nedeni: Takım listesine mülkiyet, konum ve birimli ömür hesabı; geçmiş kartına bakım ve doğrulama kaydı eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>